--- a/data/duration/storico_duration_fondi.xlsx
+++ b/data/duration/storico_duration_fondi.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr codeName="Questa_cartella_di_lavoro"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\RISK MANAGEMENT\Dati Risk Anima e CI -nominati sui dati di fine mese\rating obb fondi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9477FF7-7B5A-448B-B135-78C545AEC8E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEB1857D-4347-4E79-828D-535F8CF68AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="12">
   <si>
     <t>Data</t>
   </si>
@@ -441,17 +441,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Foglio1"/>
-  <dimension ref="A1:E351"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E428"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.28515625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.86328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.26953125" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.26953125" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -468,7 +468,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A2" s="2">
         <v>45660</v>
       </c>
@@ -485,7 +485,7 @@
         <v>-0.26</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A3" s="2">
         <v>45660</v>
       </c>
@@ -502,7 +502,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A4" s="2">
         <v>45660</v>
       </c>
@@ -519,7 +519,7 @@
         <v>-7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A5" s="2">
         <v>45660</v>
       </c>
@@ -536,7 +536,7 @@
         <v>0.94</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A6" s="2">
         <v>45660</v>
       </c>
@@ -547,7 +547,7 @@
         <v>4.79</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A7" s="2">
         <v>45660</v>
       </c>
@@ -564,7 +564,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A8" s="2">
         <v>45660</v>
       </c>
@@ -581,7 +581,7 @@
         <v>1.77</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A9" s="2">
         <v>45667</v>
       </c>
@@ -598,7 +598,7 @@
         <v>-0.26</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A10" s="2">
         <v>45667</v>
       </c>
@@ -615,7 +615,7 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A11" s="2">
         <v>45667</v>
       </c>
@@ -632,7 +632,7 @@
         <v>-0.08</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A12" s="2">
         <v>45667</v>
       </c>
@@ -649,7 +649,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A13" s="2">
         <v>45667</v>
       </c>
@@ -660,7 +660,7 @@
         <v>4.7300000000000004</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A14" s="2">
         <v>45667</v>
       </c>
@@ -677,7 +677,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A15" s="2">
         <v>45667</v>
       </c>
@@ -694,7 +694,7 @@
         <v>1.61</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A16" s="2">
         <v>45674</v>
       </c>
@@ -711,7 +711,7 @@
         <v>-0.26</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A17" s="2">
         <v>45674</v>
       </c>
@@ -728,7 +728,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A18" s="2">
         <v>45674</v>
       </c>
@@ -745,7 +745,7 @@
         <v>-0.02</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A19" s="2">
         <v>45674</v>
       </c>
@@ -762,7 +762,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A20" s="2">
         <v>45674</v>
       </c>
@@ -773,7 +773,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A21" s="2">
         <v>45674</v>
       </c>
@@ -790,7 +790,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A22" s="2">
         <v>45674</v>
       </c>
@@ -807,7 +807,7 @@
         <v>1.65</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A23" s="2">
         <v>45681</v>
       </c>
@@ -824,7 +824,7 @@
         <v>-0.26</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A24" s="2">
         <v>45681</v>
       </c>
@@ -841,7 +841,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A25" s="2">
         <v>45681</v>
       </c>
@@ -858,7 +858,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A26" s="2">
         <v>45681</v>
       </c>
@@ -875,7 +875,7 @@
         <v>0.66</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A27" s="2">
         <v>45681</v>
       </c>
@@ -886,7 +886,7 @@
         <v>4.72</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A28" s="2">
         <v>45681</v>
       </c>
@@ -903,7 +903,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A29" s="2">
         <v>45681</v>
       </c>
@@ -920,7 +920,7 @@
         <v>1.73</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A30" s="2">
         <v>45688</v>
       </c>
@@ -937,7 +937,7 @@
         <v>-0.26</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A31" s="2">
         <v>45688</v>
       </c>
@@ -954,7 +954,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A32" s="2">
         <v>45688</v>
       </c>
@@ -971,7 +971,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A33" s="2">
         <v>45688</v>
       </c>
@@ -988,7 +988,7 @@
         <v>0.67</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A34" s="2">
         <v>45688</v>
       </c>
@@ -999,7 +999,7 @@
         <v>4.74</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A35" s="2">
         <v>45688</v>
       </c>
@@ -1016,7 +1016,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A36" s="2">
         <v>45688</v>
       </c>
@@ -1033,7 +1033,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A37" s="2">
         <v>45695</v>
       </c>
@@ -1050,7 +1050,7 @@
         <v>-0.36</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A38" s="2">
         <v>45695</v>
       </c>
@@ -1067,7 +1067,7 @@
         <v>1.37</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A39" s="2">
         <v>45695</v>
       </c>
@@ -1084,7 +1084,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A40" s="2">
         <v>45695</v>
       </c>
@@ -1101,7 +1101,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A41" s="2">
         <v>45695</v>
       </c>
@@ -1112,7 +1112,7 @@
         <v>4.88</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A42" s="2">
         <v>45695</v>
       </c>
@@ -1129,7 +1129,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A43" s="2">
         <v>45695</v>
       </c>
@@ -1146,7 +1146,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A44" s="2">
         <v>45702</v>
       </c>
@@ -1163,7 +1163,7 @@
         <v>-0.35</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A45" s="2">
         <v>45702</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>1.56</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A46" s="2">
         <v>45702</v>
       </c>
@@ -1197,7 +1197,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A47" s="2">
         <v>45702</v>
       </c>
@@ -1214,7 +1214,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A48" s="2">
         <v>45702</v>
       </c>
@@ -1225,7 +1225,7 @@
         <v>4.8499999999999996</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A49" s="2">
         <v>45702</v>
       </c>
@@ -1242,7 +1242,7 @@
         <v>1.01</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A50" s="2">
         <v>45702</v>
       </c>
@@ -1259,7 +1259,7 @@
         <v>1.69</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A51" s="2">
         <v>45707</v>
       </c>
@@ -1276,7 +1276,7 @@
         <v>-0.35</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A52" s="2">
         <v>45707</v>
       </c>
@@ -1293,7 +1293,7 @@
         <v>1.67</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A53" s="2">
         <v>45707</v>
       </c>
@@ -1310,7 +1310,7 @@
         <v>0.26</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A54" s="2">
         <v>45707</v>
       </c>
@@ -1327,7 +1327,7 @@
         <v>0.87</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A55" s="2">
         <v>45707</v>
       </c>
@@ -1338,7 +1338,7 @@
         <v>4.8</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A56" s="2">
         <v>45707</v>
       </c>
@@ -1355,7 +1355,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A57" s="2">
         <v>45707</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>2.02</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A58" s="2">
         <v>45709</v>
       </c>
@@ -1389,7 +1389,7 @@
         <v>-0.35</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A59" s="2">
         <v>45709</v>
       </c>
@@ -1406,7 +1406,7 @@
         <v>1.87</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A60" s="2">
         <v>45709</v>
       </c>
@@ -1423,7 +1423,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A61" s="2">
         <v>45709</v>
       </c>
@@ -1440,7 +1440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A62" s="2">
         <v>45709</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>4.8099999999999996</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A63" s="2">
         <v>45709</v>
       </c>
@@ -1468,7 +1468,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A64" s="2">
         <v>45709</v>
       </c>
@@ -1485,7 +1485,7 @@
         <v>2.11</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A65" s="2">
         <v>45716</v>
       </c>
@@ -1502,7 +1502,7 @@
         <v>-0.1</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A66" s="2">
         <v>45716</v>
       </c>
@@ -1519,7 +1519,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A67" s="2">
         <v>45716</v>
       </c>
@@ -1536,7 +1536,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A68" s="2">
         <v>45716</v>
       </c>
@@ -1553,7 +1553,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A69" s="2">
         <v>45716</v>
       </c>
@@ -1564,7 +1564,7 @@
         <v>4.84</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A70" s="2">
         <v>45716</v>
       </c>
@@ -1581,7 +1581,7 @@
         <v>1.71</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A71" s="2">
         <v>45716</v>
       </c>
@@ -1598,7 +1598,7 @@
         <v>2.21</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A72" s="2">
         <v>45723</v>
       </c>
@@ -1615,7 +1615,7 @@
         <v>-0.19</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A73" s="2">
         <v>45723</v>
       </c>
@@ -1632,7 +1632,7 @@
         <v>1.85</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A74" s="2">
         <v>45723</v>
       </c>
@@ -1649,7 +1649,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A75" s="2">
         <v>45723</v>
       </c>
@@ -1666,7 +1666,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A76" s="2">
         <v>45723</v>
       </c>
@@ -1677,7 +1677,7 @@
         <v>4.71</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A77" s="2">
         <v>45723</v>
       </c>
@@ -1694,7 +1694,7 @@
         <v>1.51</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A78" s="2">
         <v>45723</v>
       </c>
@@ -1711,7 +1711,7 @@
         <v>2.39</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A79" s="2">
         <v>45730</v>
       </c>
@@ -1728,7 +1728,7 @@
         <v>-0.19</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A80" s="2">
         <v>45730</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v>2.04</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A81" s="2">
         <v>45730</v>
       </c>
@@ -1762,7 +1762,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A82" s="2">
         <v>45730</v>
       </c>
@@ -1779,7 +1779,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A83" s="2">
         <v>45730</v>
       </c>
@@ -1790,7 +1790,7 @@
         <v>4.67</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A84" s="2">
         <v>45730</v>
       </c>
@@ -1807,7 +1807,7 @@
         <v>1.66</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A85" s="2">
         <v>45730</v>
       </c>
@@ -1824,7 +1824,7 @@
         <v>2.4300000000000002</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A86" s="2">
         <v>45737</v>
       </c>
@@ -1841,7 +1841,7 @@
         <v>-0.19</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A87" s="2">
         <v>45737</v>
       </c>
@@ -1858,7 +1858,7 @@
         <v>2.08</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A88" s="2">
         <v>45737</v>
       </c>
@@ -1875,7 +1875,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A89" s="2">
         <v>45737</v>
       </c>
@@ -1892,7 +1892,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A90" s="2">
         <v>45737</v>
       </c>
@@ -1903,7 +1903,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A91" s="2">
         <v>45737</v>
       </c>
@@ -1920,7 +1920,7 @@
         <v>1.68</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A92" s="2">
         <v>45737</v>
       </c>
@@ -1937,7 +1937,7 @@
         <v>2.46</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A93" s="2">
         <v>45744</v>
       </c>
@@ -1954,7 +1954,7 @@
         <v>-0.19</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A94" s="2">
         <v>45744</v>
       </c>
@@ -1971,7 +1971,7 @@
         <v>2.14</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A95" s="2">
         <v>45744</v>
       </c>
@@ -1988,7 +1988,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A96" s="2">
         <v>45744</v>
       </c>
@@ -2005,7 +2005,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A97" s="2">
         <v>45744</v>
       </c>
@@ -2016,7 +2016,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A98" s="2">
         <v>45744</v>
       </c>
@@ -2033,7 +2033,7 @@
         <v>1.73</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A99" s="2">
         <v>45744</v>
       </c>
@@ -2050,7 +2050,7 @@
         <v>2.52</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A100" s="2">
         <v>45747</v>
       </c>
@@ -2067,7 +2067,7 @@
         <v>-0.19</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A101" s="2">
         <v>45747</v>
       </c>
@@ -2084,7 +2084,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A102" s="2">
         <v>45747</v>
       </c>
@@ -2101,7 +2101,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A103" s="2">
         <v>45747</v>
       </c>
@@ -2118,7 +2118,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A104" s="2">
         <v>45747</v>
       </c>
@@ -2129,7 +2129,7 @@
         <v>4.74</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A105" s="2">
         <v>45747</v>
       </c>
@@ -2146,7 +2146,7 @@
         <v>1.84</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A106" s="2">
         <v>45747</v>
       </c>
@@ -2163,7 +2163,7 @@
         <v>2.71</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A107" s="2">
         <v>45751</v>
       </c>
@@ -2180,7 +2180,7 @@
         <v>-0.27</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A108" s="2">
         <v>45751</v>
       </c>
@@ -2197,7 +2197,7 @@
         <v>2.0099999999999998</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A109" s="2">
         <v>45751</v>
       </c>
@@ -2214,7 +2214,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A110" s="2">
         <v>45751</v>
       </c>
@@ -2231,7 +2231,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A111" s="2">
         <v>45751</v>
       </c>
@@ -2242,7 +2242,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A112" s="2">
         <v>45751</v>
       </c>
@@ -2259,7 +2259,7 @@
         <v>1.69</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A113" s="2">
         <v>45751</v>
       </c>
@@ -2276,7 +2276,7 @@
         <v>2.73</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A114" s="2">
         <v>45758</v>
       </c>
@@ -2293,7 +2293,7 @@
         <v>-0.26</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A115" s="2">
         <v>45758</v>
       </c>
@@ -2310,7 +2310,7 @@
         <v>2.09</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A116" s="2">
         <v>45758</v>
       </c>
@@ -2327,7 +2327,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A117" s="2">
         <v>45758</v>
       </c>
@@ -2344,7 +2344,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A118" s="2">
         <v>45758</v>
       </c>
@@ -2355,7 +2355,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A119" s="2">
         <v>45758</v>
       </c>
@@ -2372,7 +2372,7 @@
         <v>1.74</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A120" s="2">
         <v>45758</v>
       </c>
@@ -2389,7 +2389,7 @@
         <v>2.74</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A121" s="2">
         <v>45765</v>
       </c>
@@ -2406,7 +2406,7 @@
         <v>-0.27</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A122" s="2">
         <v>45765</v>
       </c>
@@ -2423,7 +2423,7 @@
         <v>2.11</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A123" s="2">
         <v>45765</v>
       </c>
@@ -2440,7 +2440,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A124" s="2">
         <v>45765</v>
       </c>
@@ -2457,7 +2457,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A125" s="2">
         <v>45765</v>
       </c>
@@ -2468,7 +2468,7 @@
         <v>4.92</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A126" s="2">
         <v>45765</v>
       </c>
@@ -2485,7 +2485,7 @@
         <v>1.39</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A127" s="2">
         <v>45765</v>
       </c>
@@ -2502,7 +2502,7 @@
         <v>2.4300000000000002</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A128" s="2">
         <v>45771</v>
       </c>
@@ -2519,7 +2519,7 @@
         <v>-0.27</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A129" s="2">
         <v>45771</v>
       </c>
@@ -2536,7 +2536,7 @@
         <v>2.11</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A130" s="2">
         <v>45771</v>
       </c>
@@ -2553,7 +2553,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A131" s="2">
         <v>45771</v>
       </c>
@@ -2570,7 +2570,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A132" s="2">
         <v>45771</v>
       </c>
@@ -2581,7 +2581,7 @@
         <v>4.92</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A133" s="2">
         <v>45771</v>
       </c>
@@ -2598,7 +2598,7 @@
         <v>1.39</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A134" s="2">
         <v>45771</v>
       </c>
@@ -2615,7 +2615,7 @@
         <v>2.44</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A135" s="2">
         <v>45777</v>
       </c>
@@ -2632,7 +2632,7 @@
         <v>-0.27</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A136" s="2">
         <v>45777</v>
       </c>
@@ -2649,7 +2649,7 @@
         <v>2.19</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A137" s="2">
         <v>45777</v>
       </c>
@@ -2666,7 +2666,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A138" s="2">
         <v>45777</v>
       </c>
@@ -2683,7 +2683,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A139" s="2">
         <v>45777</v>
       </c>
@@ -2694,7 +2694,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A140" s="2">
         <v>45777</v>
       </c>
@@ -2711,7 +2711,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A141" s="2">
         <v>45777</v>
       </c>
@@ -2728,7 +2728,7 @@
         <v>2.41</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A142" s="2">
         <v>45786</v>
       </c>
@@ -2745,7 +2745,7 @@
         <v>-0.36</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A143" s="2">
         <v>45786</v>
       </c>
@@ -2762,7 +2762,7 @@
         <v>2.16</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A144" s="2">
         <v>45786</v>
       </c>
@@ -2779,7 +2779,7 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A145" s="2">
         <v>45786</v>
       </c>
@@ -2796,7 +2796,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A146" s="2">
         <v>45786</v>
       </c>
@@ -2807,7 +2807,7 @@
         <v>4.8499999999999996</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A147" s="2">
         <v>45786</v>
       </c>
@@ -2824,7 +2824,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A148" s="2">
         <v>45786</v>
       </c>
@@ -2841,7 +2841,7 @@
         <v>2.33</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A149" s="2">
         <v>45793</v>
       </c>
@@ -2858,7 +2858,7 @@
         <v>-0.36</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A150" s="2">
         <v>45793</v>
       </c>
@@ -2875,7 +2875,7 @@
         <v>2.16</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A151" s="2">
         <v>45793</v>
       </c>
@@ -2892,7 +2892,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A152" s="2">
         <v>45793</v>
       </c>
@@ -2909,7 +2909,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A153" s="2">
         <v>45793</v>
       </c>
@@ -2920,7 +2920,7 @@
         <v>4.83</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A154" s="2">
         <v>45793</v>
       </c>
@@ -2937,7 +2937,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A155" s="2">
         <v>45793</v>
       </c>
@@ -2954,7 +2954,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A156" s="2">
         <v>45800</v>
       </c>
@@ -2971,7 +2971,7 @@
         <v>-0.36</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A157" s="2">
         <v>45800</v>
       </c>
@@ -2988,7 +2988,7 @@
         <v>2.09</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A158" s="2">
         <v>45800</v>
       </c>
@@ -3005,7 +3005,7 @@
         <v>0.22</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A159" s="2">
         <v>45800</v>
       </c>
@@ -3022,7 +3022,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A160" s="2">
         <v>45800</v>
       </c>
@@ -3033,7 +3033,7 @@
         <v>4.8099999999999996</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A161" s="2">
         <v>45800</v>
       </c>
@@ -3050,7 +3050,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A162" s="2">
         <v>45800</v>
       </c>
@@ -3067,7 +3067,7 @@
         <v>2.3199999999999998</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A163" s="2">
         <v>45807</v>
       </c>
@@ -3084,7 +3084,7 @@
         <v>-0.12</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A164" s="2">
         <v>45807</v>
       </c>
@@ -3101,7 +3101,7 @@
         <v>1.92</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A165" s="2">
         <v>45807</v>
       </c>
@@ -3118,7 +3118,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A166" s="2">
         <v>45807</v>
       </c>
@@ -3135,7 +3135,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A167" s="2">
         <v>45807</v>
       </c>
@@ -3146,7 +3146,7 @@
         <v>4.88</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A168" s="2">
         <v>45807</v>
       </c>
@@ -3163,7 +3163,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A169" s="2">
         <v>45807</v>
       </c>
@@ -3180,7 +3180,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A170" s="2">
         <v>45814</v>
       </c>
@@ -3197,7 +3197,7 @@
         <v>-0.19</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A171" s="2">
         <v>45814</v>
       </c>
@@ -3214,7 +3214,7 @@
         <v>1.81</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A172" s="2">
         <v>45814</v>
       </c>
@@ -3231,7 +3231,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A173" s="2">
         <v>45814</v>
       </c>
@@ -3248,7 +3248,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A174" s="2">
         <v>45814</v>
       </c>
@@ -3259,7 +3259,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A175" s="2">
         <v>45814</v>
       </c>
@@ -3276,7 +3276,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A176" s="2">
         <v>45814</v>
       </c>
@@ -3293,7 +3293,7 @@
         <v>1.64</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A177" s="2">
         <v>45821</v>
       </c>
@@ -3310,7 +3310,7 @@
         <v>-0.19</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A178" s="2">
         <v>45821</v>
       </c>
@@ -3327,7 +3327,7 @@
         <v>1.86</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A179" s="2">
         <v>45821</v>
       </c>
@@ -3344,7 +3344,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A180" s="2">
         <v>45821</v>
       </c>
@@ -3361,7 +3361,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A181" s="2">
         <v>45821</v>
       </c>
@@ -3372,7 +3372,7 @@
         <v>4.88</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A182" s="2">
         <v>45821</v>
       </c>
@@ -3389,7 +3389,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A183" s="2">
         <v>45821</v>
       </c>
@@ -3406,7 +3406,7 @@
         <v>1.65</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A184" s="2">
         <v>45828</v>
       </c>
@@ -3423,7 +3423,7 @@
         <v>-0.19</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A185" s="2">
         <v>45828</v>
       </c>
@@ -3440,7 +3440,7 @@
         <v>2.0099999999999998</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A186" s="2">
         <v>45828</v>
       </c>
@@ -3457,7 +3457,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A187" s="2">
         <v>45828</v>
       </c>
@@ -3474,7 +3474,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A188" s="2">
         <v>45828</v>
       </c>
@@ -3485,7 +3485,7 @@
         <v>4.8600000000000003</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A189" s="2">
         <v>45828</v>
       </c>
@@ -3502,7 +3502,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A190" s="2">
         <v>45828</v>
       </c>
@@ -3519,7 +3519,7 @@
         <v>1.76</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A191" s="2">
         <v>45835</v>
       </c>
@@ -3536,7 +3536,7 @@
         <v>-0.2</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A192" s="2">
         <v>45835</v>
       </c>
@@ -3553,7 +3553,7 @@
         <v>2.0099999999999998</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A193" s="2">
         <v>45835</v>
       </c>
@@ -3570,7 +3570,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A194" s="2">
         <v>45835</v>
       </c>
@@ -3587,7 +3587,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A195" s="2">
         <v>45835</v>
       </c>
@@ -3598,7 +3598,7 @@
         <v>4.83</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A196" s="2">
         <v>45835</v>
       </c>
@@ -3615,7 +3615,7 @@
         <v>1.32</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A197" s="2">
         <v>45835</v>
       </c>
@@ -3632,7 +3632,7 @@
         <v>1.74</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A198" s="2">
         <v>45838</v>
       </c>
@@ -3649,7 +3649,7 @@
         <v>-0.19</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A199" s="2">
         <v>45838</v>
       </c>
@@ -3666,7 +3666,7 @@
         <v>1.98</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A200" s="2">
         <v>45838</v>
       </c>
@@ -3683,7 +3683,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A201" s="2">
         <v>45838</v>
       </c>
@@ -3700,7 +3700,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A202" s="2">
         <v>45838</v>
       </c>
@@ -3711,7 +3711,7 @@
         <v>4.82</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A203" s="2">
         <v>45838</v>
       </c>
@@ -3728,7 +3728,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A204" s="2">
         <v>45838</v>
       </c>
@@ -3745,7 +3745,7 @@
         <v>1.72</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A205" s="2">
         <v>45842</v>
       </c>
@@ -3762,7 +3762,7 @@
         <v>-0.28000000000000003</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A206" s="2">
         <v>45842</v>
       </c>
@@ -3779,7 +3779,7 @@
         <v>1.97</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A207" s="2">
         <v>45842</v>
       </c>
@@ -3796,7 +3796,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A208" s="2">
         <v>45842</v>
       </c>
@@ -3813,7 +3813,7 @@
         <v>0.78</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A209" s="2">
         <v>45842</v>
       </c>
@@ -3824,7 +3824,7 @@
         <v>4.8099999999999996</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A210" s="2">
         <v>45842</v>
       </c>
@@ -3841,7 +3841,7 @@
         <v>1.27</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A211" s="2">
         <v>45842</v>
       </c>
@@ -3858,7 +3858,7 @@
         <v>1.68</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A212" s="2">
         <v>45849</v>
       </c>
@@ -3875,7 +3875,7 @@
         <v>-0.28000000000000003</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A213" s="2">
         <v>45849</v>
       </c>
@@ -3892,7 +3892,7 @@
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A214" s="2">
         <v>45849</v>
       </c>
@@ -3909,7 +3909,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A215" s="2">
         <v>45849</v>
       </c>
@@ -3926,7 +3926,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A216" s="2">
         <v>45849</v>
       </c>
@@ -3937,7 +3937,7 @@
         <v>4.75</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A217" s="2">
         <v>45849</v>
       </c>
@@ -3954,7 +3954,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A218" s="2">
         <v>45849</v>
       </c>
@@ -3971,7 +3971,7 @@
         <v>1.66</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A219" s="2">
         <v>45856</v>
       </c>
@@ -3988,7 +3988,7 @@
         <v>-0.28000000000000003</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A220" s="2">
         <v>45856</v>
       </c>
@@ -4005,7 +4005,7 @@
         <v>2.06</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A221" s="2">
         <v>45856</v>
       </c>
@@ -4022,7 +4022,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A222" s="2">
         <v>45856</v>
       </c>
@@ -4039,7 +4039,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A223" s="2">
         <v>45856</v>
       </c>
@@ -4050,7 +4050,7 @@
         <v>4.74</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A224" s="2">
         <v>45856</v>
       </c>
@@ -4067,7 +4067,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A225" s="2">
         <v>45856</v>
       </c>
@@ -4084,7 +4084,7 @@
         <v>1.65</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A226" s="2">
         <v>45863</v>
       </c>
@@ -4101,7 +4101,7 @@
         <v>-0.26</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A227" s="2">
         <v>45863</v>
       </c>
@@ -4118,7 +4118,7 @@
         <v>2.09</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A228" s="2">
         <v>45863</v>
       </c>
@@ -4135,7 +4135,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A229" s="2">
         <v>45863</v>
       </c>
@@ -4152,7 +4152,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A230" s="2">
         <v>45863</v>
       </c>
@@ -4163,7 +4163,7 @@
         <v>4.72</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A231" s="2">
         <v>45863</v>
       </c>
@@ -4180,7 +4180,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A232" s="2">
         <v>45863</v>
       </c>
@@ -4197,7 +4197,7 @@
         <v>1.66</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A233" s="2">
         <v>45869</v>
       </c>
@@ -4214,7 +4214,7 @@
         <v>-0.25</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A234" s="2">
         <v>45869</v>
       </c>
@@ -4231,7 +4231,7 @@
         <v>2.0699999999999998</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A235" s="2">
         <v>45869</v>
       </c>
@@ -4248,7 +4248,7 @@
         <v>-0.04</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A236" s="2">
         <v>45869</v>
       </c>
@@ -4265,7 +4265,7 @@
         <v>0.91</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A237" s="2">
         <v>45869</v>
       </c>
@@ -4276,7 +4276,7 @@
         <v>4.7300000000000004</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A238" s="2">
         <v>45869</v>
       </c>
@@ -4293,7 +4293,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A239" s="2">
         <v>45869</v>
       </c>
@@ -4310,7 +4310,7 @@
         <v>1.73</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A240" s="2">
         <v>45870</v>
       </c>
@@ -4327,7 +4327,7 @@
         <v>-0.35</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A241" s="2">
         <v>45870</v>
       </c>
@@ -4344,7 +4344,7 @@
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A242" s="2">
         <v>45870</v>
       </c>
@@ -4361,7 +4361,7 @@
         <v>-0.06</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A243" s="2">
         <v>45870</v>
       </c>
@@ -4378,7 +4378,7 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A244" s="2">
         <v>45870</v>
       </c>
@@ -4389,7 +4389,7 @@
         <v>4.72</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A245" s="2">
         <v>45870</v>
       </c>
@@ -4406,7 +4406,7 @@
         <v>1.42</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A246" s="2">
         <v>45870</v>
       </c>
@@ -4423,7 +4423,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A247" s="2">
         <v>45877</v>
       </c>
@@ -4440,7 +4440,7 @@
         <v>-0.35</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A248" s="2">
         <v>45877</v>
       </c>
@@ -4457,7 +4457,7 @@
         <v>2.06</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A249" s="2">
         <v>45877</v>
       </c>
@@ -4474,7 +4474,7 @@
         <v>-0.06</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A250" s="2">
         <v>45877</v>
       </c>
@@ -4491,7 +4491,7 @@
         <v>0.89</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A251" s="2">
         <v>45877</v>
       </c>
@@ -4502,7 +4502,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A252" s="2">
         <v>45877</v>
       </c>
@@ -4519,7 +4519,7 @@
         <v>1.42</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A253" s="2">
         <v>45877</v>
       </c>
@@ -4536,7 +4536,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A254" s="2">
         <v>45883</v>
       </c>
@@ -4553,7 +4553,7 @@
         <v>-0.34</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A255" s="2">
         <v>45883</v>
       </c>
@@ -4570,7 +4570,7 @@
         <v>2.02</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A256" s="2">
         <v>45883</v>
       </c>
@@ -4587,7 +4587,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A257" s="2">
         <v>45883</v>
       </c>
@@ -4604,7 +4604,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A258" s="2">
         <v>45883</v>
       </c>
@@ -4615,7 +4615,7 @@
         <v>4.68</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A259" s="2">
         <v>45883</v>
       </c>
@@ -4632,7 +4632,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A260" s="2">
         <v>45883</v>
       </c>
@@ -4649,7 +4649,7 @@
         <v>1.69</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A261" s="2">
         <v>45891</v>
       </c>
@@ -4666,7 +4666,7 @@
         <v>-0.34</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A262" s="2">
         <v>45891</v>
       </c>
@@ -4683,7 +4683,7 @@
         <v>2.0099999999999998</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A263" s="2">
         <v>45891</v>
       </c>
@@ -4700,7 +4700,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A264" s="2">
         <v>45891</v>
       </c>
@@ -4717,7 +4717,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A265" s="2">
         <v>45891</v>
       </c>
@@ -4728,7 +4728,7 @@
         <v>4.63</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A266" s="2">
         <v>45891</v>
       </c>
@@ -4745,7 +4745,7 @@
         <v>1.39</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A267" s="2">
         <v>45891</v>
       </c>
@@ -4762,7 +4762,7 @@
         <v>1.67</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A268" s="2">
         <v>45898</v>
       </c>
@@ -4779,7 +4779,7 @@
         <v>-0.16</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A269" s="2">
         <v>45898</v>
       </c>
@@ -4796,7 +4796,7 @@
         <v>1.99</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A270" s="2">
         <v>45898</v>
       </c>
@@ -4813,7 +4813,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A271" s="2">
         <v>45898</v>
       </c>
@@ -4830,7 +4830,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A272" s="2">
         <v>45898</v>
       </c>
@@ -4841,7 +4841,7 @@
         <v>4.6399999999999997</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A273" s="2">
         <v>45898</v>
       </c>
@@ -4858,7 +4858,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A274" s="2">
         <v>45898</v>
       </c>
@@ -4875,7 +4875,7 @@
         <v>1.67</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A275" s="2">
         <v>45905</v>
       </c>
@@ -4892,7 +4892,7 @@
         <v>-0.24</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A276" s="2">
         <v>45905</v>
       </c>
@@ -4909,7 +4909,7 @@
         <v>2.0299999999999998</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A277" s="2">
         <v>45905</v>
       </c>
@@ -4926,7 +4926,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A278" s="2">
         <v>45905</v>
       </c>
@@ -4943,7 +4943,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A279" s="2">
         <v>45905</v>
       </c>
@@ -4954,7 +4954,7 @@
         <v>4.6500000000000004</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A280" s="2">
         <v>45905</v>
       </c>
@@ -4971,7 +4971,7 @@
         <v>1.36</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A281" s="2">
         <v>45905</v>
       </c>
@@ -4988,7 +4988,7 @@
         <v>1.77</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A282" s="2">
         <v>45912</v>
       </c>
@@ -5005,7 +5005,7 @@
         <v>-0.23501849759949434</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A283" s="2">
         <v>45912</v>
       </c>
@@ -5022,7 +5022,7 @@
         <v>2.0453738761404434</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A284" s="2">
         <v>45912</v>
       </c>
@@ -5039,7 +5039,7 @@
         <v>1.4690795299679129</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A285" s="2">
         <v>45912</v>
       </c>
@@ -5050,7 +5050,7 @@
         <v>4.6363808950972771</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A286" s="2">
         <v>45912</v>
       </c>
@@ -5067,7 +5067,7 @@
         <v>1.262581287092619</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A287" s="2">
         <v>45912</v>
       </c>
@@ -5084,7 +5084,7 @@
         <v>0.96059246011396571</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A288" s="2">
         <v>45912</v>
       </c>
@@ -5101,7 +5101,7 @@
         <v>9.8019311945193532E-2</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A289" s="2">
         <v>45915</v>
       </c>
@@ -5118,7 +5118,7 @@
         <v>-0.23505897193083708</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A290" s="2">
         <v>45915</v>
       </c>
@@ -5135,7 +5135,7 @@
         <v>2.0174998233575216</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A291" s="2">
         <v>45915</v>
       </c>
@@ -5152,7 +5152,7 @@
         <v>1.478789370031139</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A292" s="2">
         <v>45915</v>
       </c>
@@ -5163,7 +5163,7 @@
         <v>4.6450832024664548</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A293" s="2">
         <v>45915</v>
       </c>
@@ -5180,7 +5180,7 @@
         <v>1.2709333361241626</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A294" s="2">
         <v>45915</v>
       </c>
@@ -5197,7 +5197,7 @@
         <v>0.97064247806082538</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A295" s="2">
         <v>45915</v>
       </c>
@@ -5214,7 +5214,7 @@
         <v>9.7858968265405633E-2</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A296" s="2">
         <v>45919</v>
       </c>
@@ -5231,7 +5231,7 @@
         <v>-0.23526456987253413</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A297" s="2">
         <v>45919</v>
       </c>
@@ -5248,7 +5248,7 @@
         <v>1.9937658938577574</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A298" s="2">
         <v>45919</v>
       </c>
@@ -5265,7 +5265,7 @@
         <v>1.4599789706137996</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A299" s="2">
         <v>45919</v>
       </c>
@@ -5276,7 +5276,7 @@
         <v>4.6064135878182064</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A300" s="2">
         <v>45919</v>
       </c>
@@ -5293,7 +5293,7 @@
         <v>1.2552233621935009</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A301" s="2">
         <v>45919</v>
       </c>
@@ -5310,7 +5310,7 @@
         <v>0.95604691843888912</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A302" s="2">
         <v>45919</v>
       </c>
@@ -5327,7 +5327,7 @@
         <v>9.7625622060256267E-2</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A303" s="2">
         <v>45923</v>
       </c>
@@ -5344,7 +5344,7 @@
         <v>-0.15840648035704769</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A304" s="2">
         <v>45923</v>
       </c>
@@ -5361,7 +5361,7 @@
         <v>2.0479816868780345</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A305" s="2">
         <v>45923</v>
       </c>
@@ -5378,7 +5378,7 @@
         <v>1.688751760062372</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A306" s="2">
         <v>45923</v>
       </c>
@@ -5389,7 +5389,7 @@
         <v>4.595712532877184</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A307" s="2">
         <v>45923</v>
       </c>
@@ -5406,7 +5406,7 @@
         <v>1.2516779475079209</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A308" s="2">
         <v>45923</v>
       </c>
@@ -5423,7 +5423,7 @@
         <v>1.0086831653437267</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A309" s="2">
         <v>45923</v>
       </c>
@@ -5440,7 +5440,7 @@
         <v>6.2883747948420998E-2</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A310" s="2">
         <v>45926</v>
       </c>
@@ -5457,7 +5457,7 @@
         <v>-7.6425837661282414E-2</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A311" s="2">
         <v>45926</v>
       </c>
@@ -5474,7 +5474,7 @@
         <v>2.0547060013270899</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A312" s="2">
         <v>45926</v>
       </c>
@@ -5491,7 +5491,7 @@
         <v>1.6890967970372568</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A313" s="2">
         <v>45926</v>
       </c>
@@ -5502,7 +5502,7 @@
         <v>4.5871541252480048</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A314" s="2">
         <v>45926</v>
       </c>
@@ -5519,7 +5519,7 @@
         <v>1.2536886880169735</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A315" s="2">
         <v>45926</v>
       </c>
@@ -5536,7 +5536,7 @@
         <v>1.0115026836410621</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A316" s="2">
         <v>45926</v>
       </c>
@@ -5553,7 +5553,7 @@
         <v>0.27859615159830153</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A317" s="2">
         <v>45930</v>
       </c>
@@ -5570,7 +5570,7 @@
         <v>-0.1649343682657386</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A318" s="2">
         <v>45930</v>
       </c>
@@ -5587,7 +5587,7 @@
         <v>1.9293789158379484</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A319" s="2">
         <v>45930</v>
       </c>
@@ -5604,7 +5604,7 @@
         <v>1.5708986554280058</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A320" s="2">
         <v>45930</v>
       </c>
@@ -5615,7 +5615,7 @@
         <v>4.605848951080552</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A321" s="2">
         <v>45930</v>
       </c>
@@ -5632,7 +5632,7 @@
         <v>1.1346515468220071</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A322" s="2">
         <v>45930</v>
       </c>
@@ -5649,7 +5649,7 @@
         <v>0.88586192436264177</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A323" s="2">
         <v>45930</v>
       </c>
@@ -5666,7 +5666,7 @@
         <v>0.17008066773629671</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A324" s="2">
         <v>45932</v>
       </c>
@@ -5683,7 +5683,7 @@
         <v>-0.16507853602782835</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A325" s="2">
         <v>45932</v>
       </c>
@@ -5700,7 +5700,7 @@
         <v>1.9884735377115623</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A326" s="2">
         <v>45932</v>
       </c>
@@ -5717,7 +5717,7 @@
         <v>1.3681468000229078</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A327" s="2">
         <v>45932</v>
       </c>
@@ -5728,7 +5728,7 @@
         <v>4.5946659456823626</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A328" s="2">
         <v>45932</v>
       </c>
@@ -5745,7 +5745,7 @@
         <v>1.1325345291674047</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A329" s="2">
         <v>45932</v>
       </c>
@@ -5762,7 +5762,7 @@
         <v>0.9417842975725268</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A330" s="2">
         <v>45932</v>
       </c>
@@ -5779,7 +5779,7 @@
         <v>0.16983491141191509</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A331" s="2">
         <v>45933</v>
       </c>
@@ -5796,7 +5796,7 @@
         <v>-0.1650650112459966</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A332" s="2">
         <v>45933</v>
       </c>
@@ -5813,7 +5813,7 @@
         <v>1.9979405962728469</v>
       </c>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A333" s="2">
         <v>45933</v>
       </c>
@@ -5830,7 +5830,7 @@
         <v>1.3731518945521746</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A334" s="2">
         <v>45933</v>
       </c>
@@ -5841,7 +5841,7 @@
         <v>4.5995135521241215</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A335" s="2">
         <v>45933</v>
       </c>
@@ -5858,7 +5858,7 @@
         <v>1.1381512244343517</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A336" s="2">
         <v>45933</v>
       </c>
@@ -5875,7 +5875,7 @@
         <v>0.94820116448070735</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A337" s="2">
         <v>45933</v>
       </c>
@@ -5892,7 +5892,7 @@
         <v>0.16977212530362085</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A338" s="2">
         <v>45940</v>
       </c>
@@ -5909,7 +5909,7 @@
         <v>-0.16536638759241692</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A339" s="2">
         <v>45940</v>
       </c>
@@ -5926,7 +5926,7 @@
         <v>2.0044674097791146</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A340" s="2">
         <v>45940</v>
       </c>
@@ -5943,7 +5943,7 @@
         <v>1.6832044687596701</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A341" s="2">
         <v>45940</v>
       </c>
@@ -5954,7 +5954,7 @@
         <v>4.9502945970815802</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A342" s="2">
         <v>45940</v>
       </c>
@@ -5971,7 +5971,7 @@
         <v>1.0729528275858433</v>
       </c>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A343" s="2">
         <v>45940</v>
       </c>
@@ -5988,7 +5988,7 @@
         <v>1.0431161354884573</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A344" s="2">
         <v>45940</v>
       </c>
@@ -6005,7 +6005,7 @@
         <v>0.16927143630329877</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A345" s="2">
         <v>45947</v>
       </c>
@@ -6022,7 +6022,7 @@
         <v>-0.16564180829447064</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A346" s="2">
         <v>45947</v>
       </c>
@@ -6039,7 +6039,7 @@
         <v>1.7195445397917757</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A347" s="2">
         <v>45947</v>
       </c>
@@ -6056,7 +6056,7 @@
         <v>1.6868489600337719</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A348" s="2">
         <v>45947</v>
       </c>
@@ -6067,7 +6067,7 @@
         <v>4.9668456036423354</v>
       </c>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A349" s="2">
         <v>45947</v>
       </c>
@@ -6084,7 +6084,7 @@
         <v>0.86101237175594569</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A350" s="2">
         <v>45947</v>
       </c>
@@ -6101,7 +6101,7 @@
         <v>0.76978065556890307</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A351" s="2">
         <v>45947</v>
       </c>
@@ -6116,6 +6116,1249 @@
       </c>
       <c r="E351" s="4">
         <v>0.19869792543904286</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A352" s="2">
+        <v>45951</v>
+      </c>
+      <c r="B352" t="s">
+        <v>5</v>
+      </c>
+      <c r="C352" s="4">
+        <v>0.21117355745449731</v>
+      </c>
+      <c r="D352" s="4">
+        <v>0.37683311651000001</v>
+      </c>
+      <c r="E352" s="4">
+        <v>-0.1656595590555027</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A353" s="2">
+        <v>45951</v>
+      </c>
+      <c r="B353" t="s">
+        <v>6</v>
+      </c>
+      <c r="C353" s="4">
+        <v>7.8283243590061238</v>
+      </c>
+      <c r="D353" s="4">
+        <v>6.1067532513132434</v>
+      </c>
+      <c r="E353" s="4">
+        <v>1.7215711076928804</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A354" s="2">
+        <v>45951</v>
+      </c>
+      <c r="B354" t="s">
+        <v>11</v>
+      </c>
+      <c r="C354" s="4">
+        <v>5.996809850898452</v>
+      </c>
+      <c r="D354" s="4">
+        <v>4.3059212089465095</v>
+      </c>
+      <c r="E354" s="4">
+        <v>1.6908886419519424</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A355" s="2">
+        <v>45951</v>
+      </c>
+      <c r="B355" t="s">
+        <v>9</v>
+      </c>
+      <c r="C355" s="4">
+        <v>4.9649451994383904</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A356" s="2">
+        <v>45951</v>
+      </c>
+      <c r="B356" t="s">
+        <v>10</v>
+      </c>
+      <c r="C356" s="4">
+        <v>5.453096949365051</v>
+      </c>
+      <c r="D356" s="4">
+        <v>4.5865703584062603</v>
+      </c>
+      <c r="E356" s="4">
+        <v>0.8665265909587907</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A357" s="2">
+        <v>45951</v>
+      </c>
+      <c r="B357" t="s">
+        <v>8</v>
+      </c>
+      <c r="C357" s="4">
+        <v>5.8775794233080614</v>
+      </c>
+      <c r="D357" s="4">
+        <v>5.1062910055539472</v>
+      </c>
+      <c r="E357" s="4">
+        <v>0.77128841775411416</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A358" s="2">
+        <v>45951</v>
+      </c>
+      <c r="B358" t="s">
+        <v>7</v>
+      </c>
+      <c r="C358" s="4">
+        <v>1.6543445375177501</v>
+      </c>
+      <c r="D358" s="4">
+        <v>1.4556151747356119</v>
+      </c>
+      <c r="E358" s="4">
+        <v>0.19872936278213826</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A359" s="2">
+        <v>45954</v>
+      </c>
+      <c r="B359" t="s">
+        <v>5</v>
+      </c>
+      <c r="C359" s="4">
+        <v>0.19727125821974592</v>
+      </c>
+      <c r="D359" s="4">
+        <v>0.3631786026499999</v>
+      </c>
+      <c r="E359" s="4">
+        <v>-0.16590734443025398</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A360" s="2">
+        <v>45954</v>
+      </c>
+      <c r="B360" t="s">
+        <v>6</v>
+      </c>
+      <c r="C360" s="4">
+        <v>7.7902319489721013</v>
+      </c>
+      <c r="D360" s="4">
+        <v>6.0869646978845324</v>
+      </c>
+      <c r="E360" s="4">
+        <v>1.7032672510875688</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A361" s="2">
+        <v>45954</v>
+      </c>
+      <c r="B361" t="s">
+        <v>11</v>
+      </c>
+      <c r="C361" s="4">
+        <v>5.9632315181195317</v>
+      </c>
+      <c r="D361" s="4">
+        <v>4.2880604965251079</v>
+      </c>
+      <c r="E361" s="4">
+        <v>1.6751710215944238</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A362" s="2">
+        <v>45954</v>
+      </c>
+      <c r="B362" t="s">
+        <v>9</v>
+      </c>
+      <c r="C362" s="4">
+        <v>4.9344016452412927</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A363" s="2">
+        <v>45954</v>
+      </c>
+      <c r="B363" t="s">
+        <v>10</v>
+      </c>
+      <c r="C363" s="4">
+        <v>5.42085524911188</v>
+      </c>
+      <c r="D363" s="4">
+        <v>4.5684092032304724</v>
+      </c>
+      <c r="E363" s="4">
+        <v>0.8524460458814076</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A364" s="2">
+        <v>45954</v>
+      </c>
+      <c r="B364" t="s">
+        <v>8</v>
+      </c>
+      <c r="C364" s="4">
+        <v>5.8480337488983629</v>
+      </c>
+      <c r="D364" s="4">
+        <v>5.0875734749070736</v>
+      </c>
+      <c r="E364" s="4">
+        <v>0.76046027399128935</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A365" s="2">
+        <v>45954</v>
+      </c>
+      <c r="B365" t="s">
+        <v>7</v>
+      </c>
+      <c r="C365" s="4">
+        <v>1.6397513048296948</v>
+      </c>
+      <c r="D365" s="4">
+        <v>1.4432992351395357</v>
+      </c>
+      <c r="E365" s="4">
+        <v>0.19645206969015905</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A366" s="2">
+        <v>45961</v>
+      </c>
+      <c r="B366" t="s">
+        <v>5</v>
+      </c>
+      <c r="C366" s="4">
+        <v>0.17783977472527318</v>
+      </c>
+      <c r="D366" s="4">
+        <v>0.43261549621000006</v>
+      </c>
+      <c r="E366" s="4">
+        <v>-0.25477572148472688</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A367" s="2">
+        <v>45961</v>
+      </c>
+      <c r="B367" t="s">
+        <v>6</v>
+      </c>
+      <c r="C367" s="4">
+        <v>7.7990386724251959</v>
+      </c>
+      <c r="D367" s="4">
+        <v>6.1676139679195812</v>
+      </c>
+      <c r="E367" s="4">
+        <v>1.6314247045056147</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A368" s="2">
+        <v>45961</v>
+      </c>
+      <c r="B368" t="s">
+        <v>11</v>
+      </c>
+      <c r="C368" s="4">
+        <v>5.7453583988298753</v>
+      </c>
+      <c r="D368" s="4">
+        <v>4.3651858768108553</v>
+      </c>
+      <c r="E368" s="4">
+        <v>1.38017252201902</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A369" s="2">
+        <v>45961</v>
+      </c>
+      <c r="B369" t="s">
+        <v>9</v>
+      </c>
+      <c r="C369" s="4">
+        <v>4.9264898005489641</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A370" s="2">
+        <v>45961</v>
+      </c>
+      <c r="B370" t="s">
+        <v>10</v>
+      </c>
+      <c r="C370" s="4">
+        <v>5.8337182741721438</v>
+      </c>
+      <c r="D370" s="4">
+        <v>4.6460837611394883</v>
+      </c>
+      <c r="E370" s="4">
+        <v>1.1876345130326555</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A371" s="2">
+        <v>45961</v>
+      </c>
+      <c r="B371" t="s">
+        <v>8</v>
+      </c>
+      <c r="C371" s="4">
+        <v>6.1042676327072396</v>
+      </c>
+      <c r="D371" s="4">
+        <v>5.1662650284147329</v>
+      </c>
+      <c r="E371" s="4">
+        <v>0.9380026042925067</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A372" s="2">
+        <v>45961</v>
+      </c>
+      <c r="B372" t="s">
+        <v>7</v>
+      </c>
+      <c r="C372" s="4">
+        <v>1.6206073258572011</v>
+      </c>
+      <c r="D372" s="4">
+        <v>1.5214069961152066</v>
+      </c>
+      <c r="E372" s="4">
+        <v>9.9200329741994553E-2</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A373" s="2">
+        <v>45968</v>
+      </c>
+      <c r="B373" t="s">
+        <v>5</v>
+      </c>
+      <c r="C373" s="4">
+        <v>0.15840076982466419</v>
+      </c>
+      <c r="D373" s="4">
+        <v>0.41334546860999999</v>
+      </c>
+      <c r="E373" s="4">
+        <v>-0.25494469878533577</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A374" s="2">
+        <v>45968</v>
+      </c>
+      <c r="B374" t="s">
+        <v>6</v>
+      </c>
+      <c r="C374" s="4">
+        <v>8.0034291414664906</v>
+      </c>
+      <c r="D374" s="4">
+        <v>6.1434640545658805</v>
+      </c>
+      <c r="E374" s="4">
+        <v>1.8599650869006101</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A375" s="2">
+        <v>45968</v>
+      </c>
+      <c r="B375" t="s">
+        <v>11</v>
+      </c>
+      <c r="C375" s="4">
+        <v>5.713373722420787</v>
+      </c>
+      <c r="D375" s="4">
+        <v>4.3425696418368895</v>
+      </c>
+      <c r="E375" s="4">
+        <v>1.3708040805838975</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A376" s="2">
+        <v>45968</v>
+      </c>
+      <c r="B376" t="s">
+        <v>9</v>
+      </c>
+      <c r="C376" s="4">
+        <v>4.4267282581624352</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A377" s="2">
+        <v>45968</v>
+      </c>
+      <c r="B377" t="s">
+        <v>10</v>
+      </c>
+      <c r="C377" s="4">
+        <v>6.0578245151687344</v>
+      </c>
+      <c r="D377" s="4">
+        <v>4.623228511353096</v>
+      </c>
+      <c r="E377" s="4">
+        <v>1.4345960038156385</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A378" s="2">
+        <v>45968</v>
+      </c>
+      <c r="B378" t="s">
+        <v>8</v>
+      </c>
+      <c r="C378" s="4">
+        <v>6.2090552004180815</v>
+      </c>
+      <c r="D378" s="4">
+        <v>5.1429671586053303</v>
+      </c>
+      <c r="E378" s="4">
+        <v>1.0660880418127512</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A379" s="2">
+        <v>45968</v>
+      </c>
+      <c r="B379" t="s">
+        <v>7</v>
+      </c>
+      <c r="C379" s="4">
+        <v>1.6011019166168106</v>
+      </c>
+      <c r="D379" s="4">
+        <v>1.5022136170618812</v>
+      </c>
+      <c r="E379" s="4">
+        <v>9.8888299554929393E-2</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A380" s="2">
+        <v>45975</v>
+      </c>
+      <c r="B380" t="s">
+        <v>5</v>
+      </c>
+      <c r="C380" s="4">
+        <v>0.13895574210053421</v>
+      </c>
+      <c r="D380" s="4">
+        <v>0.39417699193999994</v>
+      </c>
+      <c r="E380" s="4">
+        <v>-0.2552212498394657</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A381" s="2">
+        <v>45975</v>
+      </c>
+      <c r="B381" t="s">
+        <v>6</v>
+      </c>
+      <c r="C381" s="4">
+        <v>7.9713697518494415</v>
+      </c>
+      <c r="D381" s="4">
+        <v>6.1237644597644971</v>
+      </c>
+      <c r="E381" s="4">
+        <v>1.8476052920849444</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A382" s="2">
+        <v>45975</v>
+      </c>
+      <c r="B382" t="s">
+        <v>11</v>
+      </c>
+      <c r="C382" s="4">
+        <v>5.6838437314899544</v>
+      </c>
+      <c r="D382" s="4">
+        <v>4.3230369698767985</v>
+      </c>
+      <c r="E382" s="4">
+        <v>1.3608067616131558</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A383" s="2">
+        <v>45975</v>
+      </c>
+      <c r="B383" t="s">
+        <v>9</v>
+      </c>
+      <c r="C383" s="4">
+        <v>4.397837721703274</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A384" s="2">
+        <v>45975</v>
+      </c>
+      <c r="B384" t="s">
+        <v>10</v>
+      </c>
+      <c r="C384" s="4">
+        <v>6.1616056131795514</v>
+      </c>
+      <c r="D384" s="4">
+        <v>4.6036698254437125</v>
+      </c>
+      <c r="E384" s="4">
+        <v>1.5579357877358389</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A385" s="2">
+        <v>45975</v>
+      </c>
+      <c r="B385" t="s">
+        <v>8</v>
+      </c>
+      <c r="C385" s="4">
+        <v>6.3622564727413113</v>
+      </c>
+      <c r="D385" s="4">
+        <v>5.1233602987157756</v>
+      </c>
+      <c r="E385" s="4">
+        <v>1.2388961740255358</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A386" s="2">
+        <v>45975</v>
+      </c>
+      <c r="B386" t="s">
+        <v>7</v>
+      </c>
+      <c r="C386" s="4">
+        <v>1.5812219625998698</v>
+      </c>
+      <c r="D386" s="4">
+        <v>1.4830337509691374</v>
+      </c>
+      <c r="E386" s="4">
+        <v>9.8188211630732436E-2</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A387" s="2">
+        <v>45980</v>
+      </c>
+      <c r="B387" t="s">
+        <v>5</v>
+      </c>
+      <c r="C387" s="4">
+        <v>0.13063751996312342</v>
+      </c>
+      <c r="D387" s="4">
+        <v>0.38599299413000004</v>
+      </c>
+      <c r="E387" s="4">
+        <v>-0.25535547416687665</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A388" s="2">
+        <v>45980</v>
+      </c>
+      <c r="B388" t="s">
+        <v>6</v>
+      </c>
+      <c r="C388" s="4">
+        <v>8.0592222657206349</v>
+      </c>
+      <c r="D388" s="4">
+        <v>6.1134270411069505</v>
+      </c>
+      <c r="E388" s="4">
+        <v>1.9457952246136845</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A389" s="2">
+        <v>45980</v>
+      </c>
+      <c r="B389" t="s">
+        <v>11</v>
+      </c>
+      <c r="C389" s="4">
+        <v>5.7402650817086451</v>
+      </c>
+      <c r="D389" s="4">
+        <v>4.31337634062848</v>
+      </c>
+      <c r="E389" s="4">
+        <v>1.4268887410801652</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A390" s="2">
+        <v>45980</v>
+      </c>
+      <c r="B390" t="s">
+        <v>9</v>
+      </c>
+      <c r="C390" s="4">
+        <v>4.3908863069217565</v>
+      </c>
+    </row>
+    <row r="391" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A391" s="2">
+        <v>45980</v>
+      </c>
+      <c r="B391" t="s">
+        <v>10</v>
+      </c>
+      <c r="C391" s="4">
+        <v>6.5473855530964764</v>
+      </c>
+      <c r="D391" s="4">
+        <v>4.5939037225212296</v>
+      </c>
+      <c r="E391" s="4">
+        <v>1.9534818305752468</v>
+      </c>
+    </row>
+    <row r="392" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A392" s="2">
+        <v>45980</v>
+      </c>
+      <c r="B392" t="s">
+        <v>8</v>
+      </c>
+      <c r="C392" s="4">
+        <v>6.6389104307872078</v>
+      </c>
+      <c r="D392" s="4">
+        <v>5.1133988741744671</v>
+      </c>
+      <c r="E392" s="4">
+        <v>1.5255115566127406</v>
+      </c>
+    </row>
+    <row r="393" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A393" s="2">
+        <v>45980</v>
+      </c>
+      <c r="B393" t="s">
+        <v>7</v>
+      </c>
+      <c r="C393" s="4">
+        <v>1.5732510949612799</v>
+      </c>
+      <c r="D393" s="4">
+        <v>1.4748307091670507</v>
+      </c>
+      <c r="E393" s="4">
+        <v>9.8420385794229182E-2</v>
+      </c>
+    </row>
+    <row r="394" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A394" s="2">
+        <v>45982</v>
+      </c>
+      <c r="B394" t="s">
+        <v>5</v>
+      </c>
+      <c r="C394" s="4">
+        <v>0.11952573450268821</v>
+      </c>
+      <c r="D394" s="4">
+        <v>0.37502800535000003</v>
+      </c>
+      <c r="E394" s="4">
+        <v>-0.25550227084731181</v>
+      </c>
+    </row>
+    <row r="395" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A395" s="2">
+        <v>45982</v>
+      </c>
+      <c r="B395" t="s">
+        <v>6</v>
+      </c>
+      <c r="C395" s="4">
+        <v>8.0458698617988453</v>
+      </c>
+      <c r="D395" s="4">
+        <v>6.104960923988072</v>
+      </c>
+      <c r="E395" s="4">
+        <v>1.9409089378107733</v>
+      </c>
+    </row>
+    <row r="396" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A396" s="2">
+        <v>45982</v>
+      </c>
+      <c r="B396" t="s">
+        <v>11</v>
+      </c>
+      <c r="C396" s="4">
+        <v>5.7272325250977048</v>
+      </c>
+      <c r="D396" s="4">
+        <v>4.3041248638446774</v>
+      </c>
+      <c r="E396" s="4">
+        <v>1.4231076612530273</v>
+      </c>
+    </row>
+    <row r="397" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A397" s="2">
+        <v>45982</v>
+      </c>
+      <c r="B397" t="s">
+        <v>9</v>
+      </c>
+      <c r="C397" s="4">
+        <v>4.388409777303675</v>
+      </c>
+    </row>
+    <row r="398" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A398" s="2">
+        <v>45982</v>
+      </c>
+      <c r="B398" t="s">
+        <v>10</v>
+      </c>
+      <c r="C398" s="4">
+        <v>6.3616839328559145</v>
+      </c>
+      <c r="D398" s="4">
+        <v>4.5847746394514415</v>
+      </c>
+      <c r="E398" s="4">
+        <v>1.776909293404473</v>
+      </c>
+    </row>
+    <row r="399" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A399" s="2">
+        <v>45982</v>
+      </c>
+      <c r="B399" t="s">
+        <v>8</v>
+      </c>
+      <c r="C399" s="4">
+        <v>6.3585969326811833</v>
+      </c>
+      <c r="D399" s="4">
+        <v>5.1044964461306304</v>
+      </c>
+      <c r="E399" s="4">
+        <v>1.254100486550553</v>
+      </c>
+    </row>
+    <row r="400" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A400" s="2">
+        <v>45982</v>
+      </c>
+      <c r="B400" t="s">
+        <v>7</v>
+      </c>
+      <c r="C400" s="4">
+        <v>1.5635327927385867</v>
+      </c>
+      <c r="D400" s="4">
+        <v>1.4639073947508479</v>
+      </c>
+      <c r="E400" s="4">
+        <v>9.962539798773884E-2</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A401" s="2">
+        <v>45989</v>
+      </c>
+      <c r="B401" t="s">
+        <v>5</v>
+      </c>
+      <c r="C401" s="4">
+        <v>0.26803521753290815</v>
+      </c>
+      <c r="D401" s="4">
+        <v>0.35871712643999992</v>
+      </c>
+      <c r="E401" s="4">
+        <v>-9.0681908907091768E-2</v>
+      </c>
+    </row>
+    <row r="402" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A402" s="2">
+        <v>45989</v>
+      </c>
+      <c r="B402" t="s">
+        <v>6</v>
+      </c>
+      <c r="C402" s="4">
+        <v>8.0562562274825655</v>
+      </c>
+      <c r="D402" s="4">
+        <v>6.1328596855345099</v>
+      </c>
+      <c r="E402" s="4">
+        <v>1.9233965419480556</v>
+      </c>
+    </row>
+    <row r="403" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A403" s="2">
+        <v>45989</v>
+      </c>
+      <c r="B403" t="s">
+        <v>11</v>
+      </c>
+      <c r="C403" s="4">
+        <v>5.7216630647770979</v>
+      </c>
+      <c r="D403" s="4">
+        <v>4.3181291669619499</v>
+      </c>
+      <c r="E403" s="4">
+        <v>1.4035338978151479</v>
+      </c>
+    </row>
+    <row r="404" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A404" s="2">
+        <v>45989</v>
+      </c>
+      <c r="B404" t="s">
+        <v>9</v>
+      </c>
+      <c r="C404" s="4">
+        <v>4.4145060856719081</v>
+      </c>
+    </row>
+    <row r="405" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A405" s="2">
+        <v>45989</v>
+      </c>
+      <c r="B405" t="s">
+        <v>10</v>
+      </c>
+      <c r="C405" s="4">
+        <v>6.2225432304711514</v>
+      </c>
+      <c r="D405" s="4">
+        <v>4.6009443127135183</v>
+      </c>
+      <c r="E405" s="4">
+        <v>1.6215989177576331</v>
+      </c>
+    </row>
+    <row r="406" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A406" s="2">
+        <v>45989</v>
+      </c>
+      <c r="B406" t="s">
+        <v>8</v>
+      </c>
+      <c r="C406" s="4">
+        <v>6.5348254842030666</v>
+      </c>
+      <c r="D406" s="4">
+        <v>5.1246760641053095</v>
+      </c>
+      <c r="E406" s="4">
+        <v>1.4101494200977571</v>
+      </c>
+    </row>
+    <row r="407" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A407" s="2">
+        <v>45989</v>
+      </c>
+      <c r="B407" t="s">
+        <v>7</v>
+      </c>
+      <c r="C407" s="4">
+        <v>1.5617769104048635</v>
+      </c>
+      <c r="D407" s="4">
+        <v>1.5306214693968601</v>
+      </c>
+      <c r="E407" s="4">
+        <v>3.1155441008003493E-2</v>
+      </c>
+    </row>
+    <row r="408" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A408" s="2">
+        <v>45992</v>
+      </c>
+      <c r="B408" t="s">
+        <v>5</v>
+      </c>
+      <c r="C408" s="4">
+        <v>0.26525908904227907</v>
+      </c>
+      <c r="D408" s="4">
+        <v>0.41366409741999988</v>
+      </c>
+      <c r="E408" s="4">
+        <v>-0.1484050083777208</v>
+      </c>
+    </row>
+    <row r="409" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A409" s="2">
+        <v>45992</v>
+      </c>
+      <c r="B409" t="s">
+        <v>6</v>
+      </c>
+      <c r="C409" s="4">
+        <v>8.0326891538476648</v>
+      </c>
+      <c r="D409" s="4">
+        <v>6.1302474489726357</v>
+      </c>
+      <c r="E409" s="4">
+        <v>1.9024417048750291</v>
+      </c>
+    </row>
+    <row r="410" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A410" s="2">
+        <v>45992</v>
+      </c>
+      <c r="B410" t="s">
+        <v>11</v>
+      </c>
+      <c r="C410" s="4">
+        <v>5.6998093550665798</v>
+      </c>
+      <c r="D410" s="4">
+        <v>4.3336069670560926</v>
+      </c>
+      <c r="E410" s="4">
+        <v>1.3662023880104872</v>
+      </c>
+    </row>
+    <row r="411" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A411" s="2">
+        <v>45992</v>
+      </c>
+      <c r="B411" t="s">
+        <v>9</v>
+      </c>
+      <c r="C411" s="4">
+        <v>4.3964811641945545</v>
+      </c>
+    </row>
+    <row r="412" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A412" s="2">
+        <v>45992</v>
+      </c>
+      <c r="B412" t="s">
+        <v>10</v>
+      </c>
+      <c r="C412" s="4">
+        <v>6.2036161059358861</v>
+      </c>
+      <c r="D412" s="4">
+        <v>4.6136028863158138</v>
+      </c>
+      <c r="E412" s="4">
+        <v>1.5900132196200722</v>
+      </c>
+    </row>
+    <row r="413" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A413" s="2">
+        <v>45992</v>
+      </c>
+      <c r="B413" t="s">
+        <v>8</v>
+      </c>
+      <c r="C413" s="4">
+        <v>6.5179465936775731</v>
+      </c>
+      <c r="D413" s="4">
+        <v>5.13211384790789</v>
+      </c>
+      <c r="E413" s="4">
+        <v>1.3858327457696831</v>
+      </c>
+    </row>
+    <row r="414" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A414" s="2">
+        <v>45992</v>
+      </c>
+      <c r="B414" t="s">
+        <v>7</v>
+      </c>
+      <c r="C414" s="4">
+        <v>1.5585901365654524</v>
+      </c>
+      <c r="D414" s="4">
+        <v>1.5394090513163863</v>
+      </c>
+      <c r="E414" s="4">
+        <v>1.9181085249066143E-2</v>
+      </c>
+    </row>
+    <row r="415" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A415" s="2">
+        <v>45996</v>
+      </c>
+      <c r="B415" t="s">
+        <v>5</v>
+      </c>
+      <c r="C415" s="4">
+        <v>0.2485896814362395</v>
+      </c>
+      <c r="D415" s="4">
+        <v>0.39726667964999973</v>
+      </c>
+      <c r="E415" s="4">
+        <v>-0.14867699821376024</v>
+      </c>
+    </row>
+    <row r="416" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A416" s="2">
+        <v>45996</v>
+      </c>
+      <c r="B416" t="s">
+        <v>6</v>
+      </c>
+      <c r="C416" s="4">
+        <v>8.0412303787225277</v>
+      </c>
+      <c r="D416" s="4">
+        <v>6.1095539376019197</v>
+      </c>
+      <c r="E416" s="4">
+        <v>1.931676441120608</v>
+      </c>
+    </row>
+    <row r="417" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A417" s="2">
+        <v>45996</v>
+      </c>
+      <c r="B417" t="s">
+        <v>11</v>
+      </c>
+      <c r="C417" s="4">
+        <v>5.7011432238737152</v>
+      </c>
+      <c r="D417" s="4">
+        <v>4.3142636565313159</v>
+      </c>
+      <c r="E417" s="4">
+        <v>1.3868795673423993</v>
+      </c>
+    </row>
+    <row r="418" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A418" s="2">
+        <v>45996</v>
+      </c>
+      <c r="B418" t="s">
+        <v>9</v>
+      </c>
+      <c r="C418" s="4">
+        <v>4.3608676214814137</v>
+      </c>
+    </row>
+    <row r="419" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A419" s="2">
+        <v>45996</v>
+      </c>
+      <c r="B419" t="s">
+        <v>10</v>
+      </c>
+      <c r="C419" s="4">
+        <v>6.213285300608554</v>
+      </c>
+      <c r="D419" s="4">
+        <v>4.5940491548799827</v>
+      </c>
+      <c r="E419" s="4">
+        <v>1.6192361457285713</v>
+      </c>
+    </row>
+    <row r="420" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A420" s="2">
+        <v>45996</v>
+      </c>
+      <c r="B420" t="s">
+        <v>8</v>
+      </c>
+      <c r="C420" s="4">
+        <v>6.51449063573153</v>
+      </c>
+      <c r="D420" s="4">
+        <v>5.1121704481182508</v>
+      </c>
+      <c r="E420" s="4">
+        <v>1.4023201876132791</v>
+      </c>
+    </row>
+    <row r="421" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A421" s="2">
+        <v>45996</v>
+      </c>
+      <c r="B421" t="s">
+        <v>7</v>
+      </c>
+      <c r="C421" s="4">
+        <v>1.5415429337963826</v>
+      </c>
+      <c r="D421" s="4">
+        <v>1.5229733758268384</v>
+      </c>
+      <c r="E421" s="4">
+        <v>1.8569557969544181E-2</v>
+      </c>
+    </row>
+    <row r="422" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A422" s="2">
+        <v>46000</v>
+      </c>
+      <c r="B422" t="s">
+        <v>5</v>
+      </c>
+      <c r="C422" s="4">
+        <v>0.24303559416606255</v>
+      </c>
+      <c r="D422" s="4">
+        <v>0.39169624214999998</v>
+      </c>
+      <c r="E422" s="4">
+        <v>-0.14866064798393744</v>
+      </c>
+    </row>
+    <row r="423" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A423" s="2">
+        <v>46000</v>
+      </c>
+      <c r="B423" t="s">
+        <v>6</v>
+      </c>
+      <c r="C423" s="4">
+        <v>8.0341269929786154</v>
+      </c>
+      <c r="D423" s="4">
+        <v>6.1010829156416335</v>
+      </c>
+      <c r="E423" s="4">
+        <v>1.9330440773369819</v>
+      </c>
+    </row>
+    <row r="424" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A424" s="2">
+        <v>46000</v>
+      </c>
+      <c r="B424" t="s">
+        <v>11</v>
+      </c>
+      <c r="C424" s="4">
+        <v>5.8512842259854327</v>
+      </c>
+      <c r="D424" s="4">
+        <v>4.3067042468299768</v>
+      </c>
+      <c r="E424" s="4">
+        <v>1.544579979155456</v>
+      </c>
+    </row>
+    <row r="425" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A425" s="2">
+        <v>46000</v>
+      </c>
+      <c r="B425" t="s">
+        <v>9</v>
+      </c>
+      <c r="C425" s="4">
+        <v>4.34939468689746</v>
+      </c>
+    </row>
+    <row r="426" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A426" s="2">
+        <v>46000</v>
+      </c>
+      <c r="B426" t="s">
+        <v>10</v>
+      </c>
+      <c r="C426" s="4">
+        <v>6.2068317355682572</v>
+      </c>
+      <c r="D426" s="4">
+        <v>4.5863476757356905</v>
+      </c>
+      <c r="E426" s="4">
+        <v>1.6204840598325667</v>
+      </c>
+    </row>
+    <row r="427" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A427" s="2">
+        <v>46000</v>
+      </c>
+      <c r="B427" t="s">
+        <v>8</v>
+      </c>
+      <c r="C427" s="4">
+        <v>6.5072419170760165</v>
+      </c>
+      <c r="D427" s="4">
+        <v>5.1042058774129355</v>
+      </c>
+      <c r="E427" s="4">
+        <v>1.403036039663081</v>
+      </c>
+    </row>
+    <row r="428" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A428" s="2">
+        <v>46000</v>
+      </c>
+      <c r="B428" t="s">
+        <v>7</v>
+      </c>
+      <c r="C428" s="4">
+        <v>1.5368273470425742</v>
+      </c>
+      <c r="D428" s="4">
+        <v>1.5176291756003908</v>
+      </c>
+      <c r="E428" s="4">
+        <v>1.9198171442183387E-2</v>
       </c>
     </row>
   </sheetData>

--- a/data/duration/storico_duration_fondi.xlsx
+++ b/data/duration/storico_duration_fondi.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr codeName="Questa_cartella_di_lavoro"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\RISK MANAGEMENT\Dati Risk Anima e CI -nominati sui dati di fine mese\rating obb fondi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEB1857D-4347-4E79-828D-535F8CF68AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04B51D6B-98D2-474B-90E0-5828A258CB8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="12">
   <si>
     <t>Data</t>
   </si>
@@ -441,7 +441,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Foglio1"/>
-  <dimension ref="A1:E428"/>
+  <dimension ref="A1:E435"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="19.54296875" bestFit="1" customWidth="1"/>
@@ -7361,6 +7361,119 @@
         <v>1.9198171442183387E-2</v>
       </c>
     </row>
+    <row r="429" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A429" s="2">
+        <v>46003</v>
+      </c>
+      <c r="B429" t="s">
+        <v>5</v>
+      </c>
+      <c r="C429" s="4">
+        <v>0.2291452438797274</v>
+      </c>
+      <c r="D429" s="4">
+        <v>0.37797769824999994</v>
+      </c>
+      <c r="E429" s="4">
+        <v>-0.14883245437027254</v>
+      </c>
+    </row>
+    <row r="430" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A430" s="2">
+        <v>46003</v>
+      </c>
+      <c r="B430" t="s">
+        <v>6</v>
+      </c>
+      <c r="C430" s="4">
+        <v>8.0168807479734152</v>
+      </c>
+      <c r="D430" s="4">
+        <v>6.0859065457875712</v>
+      </c>
+      <c r="E430" s="4">
+        <v>1.930974202185844</v>
+      </c>
+    </row>
+    <row r="431" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A431" s="2">
+        <v>46003</v>
+      </c>
+      <c r="B431" t="s">
+        <v>11</v>
+      </c>
+      <c r="C431" s="4">
+        <v>5.8345133055621581</v>
+      </c>
+      <c r="D431" s="4">
+        <v>4.2919860508471919</v>
+      </c>
+      <c r="E431" s="4">
+        <v>1.5425272547149662</v>
+      </c>
+    </row>
+    <row r="432" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A432" s="2">
+        <v>46003</v>
+      </c>
+      <c r="B432" t="s">
+        <v>9</v>
+      </c>
+      <c r="C432" s="4">
+        <v>4.3342611919116933</v>
+      </c>
+    </row>
+    <row r="433" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A433" s="2">
+        <v>46003</v>
+      </c>
+      <c r="B433" t="s">
+        <v>10</v>
+      </c>
+      <c r="C433" s="4">
+        <v>6.3475391909021246</v>
+      </c>
+      <c r="D433" s="4">
+        <v>4.5715580760327059</v>
+      </c>
+      <c r="E433" s="4">
+        <v>1.7759811148694187</v>
+      </c>
+    </row>
+    <row r="434" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A434" s="2">
+        <v>46003</v>
+      </c>
+      <c r="B434" t="s">
+        <v>8</v>
+      </c>
+      <c r="C434" s="4">
+        <v>6.4920039611919327</v>
+      </c>
+      <c r="D434" s="4">
+        <v>5.0892840485984712</v>
+      </c>
+      <c r="E434" s="4">
+        <v>1.4027199125934615</v>
+      </c>
+    </row>
+    <row r="435" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A435" s="2">
+        <v>46003</v>
+      </c>
+      <c r="B435" t="s">
+        <v>7</v>
+      </c>
+      <c r="C435" s="4">
+        <v>1.7462711339972994</v>
+      </c>
+      <c r="D435" s="4">
+        <v>1.5041379075822183</v>
+      </c>
+      <c r="E435" s="4">
+        <v>0.24213322641508106</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E288">
